--- a/artfynd/A 32470-2026 artfynd.xlsx
+++ b/artfynd/A 32470-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1220,32 +1220,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>78700956</v>
+        <v>137489013</v>
       </c>
       <c r="B6" t="n">
-        <v>43438</v>
+        <v>43487</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101298</v>
+        <v>100943</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sotnätfjäril</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Melitaea diamina</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lang, 1789)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1253,18 +1253,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Munkhyttan, Vstm</t>
+          <t>Munkhyttanområdet Yta 8:16B Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507484</v>
+        <v>507485</v>
       </c>
       <c r="R6" t="n">
         <v>6607526</v>
@@ -1294,12 +1295,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-06-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-06-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,34 +1309,52 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emil Persson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emil Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78700956</t>
+          <t>https://artportalen.se/Sighting/137489013</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96219681</v>
+        <v>137489666</v>
       </c>
       <c r="B7" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,43 +1362,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Munkhyttan, Vstm</t>
+          <t>Munkhyttanområdet Yta 8:16A Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507563</v>
+        <v>507476</v>
       </c>
       <c r="R7" t="n">
-        <v>6607512</v>
+        <v>6607539</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1406,17 +1426,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>&lt;0,5 m höga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,75 +1442,94 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96219681</t>
+          <t>https://artportalen.se/Sighting/137489666</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96219699</v>
+        <v>78700956</v>
       </c>
       <c r="B8" t="n">
-        <v>106813</v>
+        <v>43438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>101298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sotnätfjäril</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Melitaea diamina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lang, 1789)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507565</v>
+        <v>507484</v>
       </c>
       <c r="R8" t="n">
-        <v>6607503</v>
+        <v>6607526</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1522,17 +1556,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2019-06-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>0,5-1 dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>2019-06-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,30 +1570,31 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96219699</t>
+          <t>https://artportalen.se/Sighting/78700956</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96219707</v>
+        <v>96219681</v>
       </c>
       <c r="B9" t="n">
         <v>106813</v>
@@ -1594,7 +1624,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1608,7 +1638,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507570</v>
+        <v>507563</v>
       </c>
       <c r="R9" t="n">
         <v>6607512</v>
@@ -1648,7 +1678,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Frisk, 3 dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5 m höga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,6 +1703,238 @@
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219681</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>96219699</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>507565</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6607503</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0,5-1 dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219699</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>96219707</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>507570</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6607512</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Frisk, 3 dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/96219707</t>
         </is>
@@ -1688,6 +1950,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
